--- a/USUARIOS SITE.xlsx
+++ b/USUARIOS SITE.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoequatorialenergia-my.sharepoint.com/personal/suene_silva_equatorialenergia_com_br/Documents/SUENE MARQUES/SITE PRODUÇÃO PERDAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoequatorialenergia-my.sharepoint.com/personal/suene_silva_equatorialenergia_com_br/Documents/SUENE MARQUES/SITE PRODUÇÃO 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_AD4D361C20488DEA4E38A0DC0CDB46605BDEDD7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F6615FD-3564-426A-B7C1-A10931604396}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_AD4D361C20488DEA4E38A0DC0CDB46605BDEDD7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCDBC911-D07E-44AD-A1B5-023D523CB48C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
   <si>
     <t>LOGIN</t>
   </si>
@@ -70,6 +81,12 @@
   </si>
   <si>
     <t>thaynara.pinheiro</t>
+  </si>
+  <si>
+    <t>brenda.caroline</t>
+  </si>
+  <si>
+    <t>gabriela.silva</t>
   </si>
 </sst>
 </file>
@@ -387,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -482,6 +499,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/USUARIOS SITE.xlsx
+++ b/USUARIOS SITE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoequatorialenergia-my.sharepoint.com/personal/suene_silva_equatorialenergia_com_br/Documents/SUENE MARQUES/SITE PRODUÇÃO 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_AD4D361C20488DEA4E38A0DC0CDB46605BDEDD7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCDBC911-D07E-44AD-A1B5-023D523CB48C}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_AD4D361C20488DEA4E38A0DC0CDB46605BDEDD7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{953A9422-8E90-4709-8365-766BE5623967}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="624" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>LOGIN</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>gabriela.silva</t>
+  </si>
+  <si>
+    <t>jaqueline.castro</t>
   </si>
 </sst>
 </file>
@@ -404,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -515,6 +518,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/USUARIOS SITE.xlsx
+++ b/USUARIOS SITE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoequatorialenergia-my.sharepoint.com/personal/suene_silva_equatorialenergia_com_br/Documents/SUENE MARQUES/SITE PRODUÇÃO 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_AD4D361C20488DEA4E38A0DC0CDB46605BDEDD7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{953A9422-8E90-4709-8365-766BE5623967}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_AD4D361C20488DEA4E38A0DC0CDB46605BDEDD7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F70DCEF-9923-46F8-AEDC-C48B53092EAD}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="624" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>LOGIN</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>jaqueline.castro</t>
+  </si>
+  <si>
+    <t>matheus.paiva</t>
   </si>
 </sst>
 </file>
@@ -407,14 +410,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -422,7 +425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -430,7 +433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -438,7 +441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -446,7 +449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -454,7 +457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -462,7 +465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -470,7 +473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -478,7 +481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -486,7 +489,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -494,7 +497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -502,7 +505,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -510,7 +513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -518,12 +521,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
